--- a/src/test/resources/FeatureFiles/TestData.xlsx
+++ b/src/test/resources/FeatureFiles/TestData.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="14">
   <si>
     <t>FirstName</t>
   </si>
@@ -75,6 +75,9 @@
   </si>
   <si>
     <t>ff8081819cd4022c019cd6a1120f0488</t>
+  </si>
+  <si>
+    <t>ff8081819cd4022c019cdbb1731d0e0c</t>
   </si>
 </sst>
 </file>
@@ -152,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -172,6 +175,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment wrapText="true"/>
     </xf>
@@ -557,13 +563,13 @@
         <v>5</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>200.0</v>
       </c>
-      <c r="E2" t="s" s="14">
-        <v>12</v>
+      <c r="E2" t="s" s="15">
+        <v>13</v>
       </c>
       <c r="F2" s="6"/>
       <c r="G2" s="7"/>
